--- a/artfynd/S 42-2022 artfynd.xlsx
+++ b/artfynd/S 42-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ41"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105379541</v>
+        <v>136640141</v>
       </c>
       <c r="B2" t="n">
-        <v>57950</v>
+        <v>92316</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,49 +691,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>3008</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stora Björksnarssjön, Ramnäs sn, Vstm</t>
+          <t>Stora Björksnarssjön O, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559154</v>
+        <v>559107</v>
       </c>
       <c r="R2" t="n">
-        <v>6632163</v>
+        <v>6632136</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,27 +748,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-12-28</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-12-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På hyggesbrännan på tall</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,33 +762,44 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Naturvårdsbränt hygge/tallskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sören Larsson, Greta Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105379541</t>
+          <t>https://artportalen.se/Sighting/136640141</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>82321213</v>
+        <v>136640147</v>
       </c>
       <c r="B3" t="n">
-        <v>57141</v>
+        <v>92065</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,49 +807,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Målsjöv-Stora Björksnarssjön, Ramnsä, Vstm, Vstm</t>
+          <t>Stora Björksnarssjön O, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559097</v>
+        <v>559107</v>
       </c>
       <c r="R3" t="n">
-        <v>6632262</v>
+        <v>6632136</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,27 +864,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-02-22</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-02-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På grusvägen</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,37 +878,44 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Naturvårdsbränt hygge/tallskog</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Skogsprojektet</t>
-        </is>
-      </c>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82321213</t>
+          <t>https://artportalen.se/Sighting/136640147</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>82321232</v>
+        <v>105379541</v>
       </c>
       <c r="B4" t="n">
-        <v>57141</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -953,49 +923,49 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Målsjöv-Stora Björksnarssjön, Ramnsä, Vstm, Vstm</t>
+          <t>Stora Björksnarssjön, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559133</v>
+        <v>559154</v>
       </c>
       <c r="R4" t="n">
-        <v>6632300</v>
+        <v>6632163</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1019,27 +989,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-02-22</t>
+          <t>2022-12-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-02-22</t>
+          <t>2022-12-28</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På grusvägen</t>
+          <t>På hyggesbrännan på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,28 +1024,24 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Skogsprojektet</t>
-        </is>
-      </c>
+          <t>Sören Larsson, Greta Larsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82321232</t>
+          <t>https://artportalen.se/Sighting/105379541</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>82321237</v>
+        <v>82321213</v>
       </c>
       <c r="B5" t="n">
         <v>57141</v>
@@ -1122,10 +1088,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559137</v>
+        <v>559097</v>
       </c>
       <c r="R5" t="n">
-        <v>6632307</v>
+        <v>6632262</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1202,13 +1168,13 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82321237</t>
+          <t>https://artportalen.se/Sighting/82321213</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>82321521</v>
+        <v>82321232</v>
       </c>
       <c r="B6" t="n">
         <v>57141</v>
@@ -1255,10 +1221,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559145</v>
+        <v>559133</v>
       </c>
       <c r="R6" t="n">
-        <v>6632322</v>
+        <v>6632300</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1335,13 +1301,13 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82321521</t>
+          <t>https://artportalen.se/Sighting/82321232</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>84024850</v>
+        <v>82321237</v>
       </c>
       <c r="B7" t="n">
         <v>57141</v>
@@ -1374,7 +1340,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1384,17 +1350,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>St Björksnarssjön Ö skogen, Ramnäs, Vstm, Vstm</t>
+          <t>Målsjöv-Stora Björksnarssjön, Ramnsä, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559053</v>
+        <v>559137</v>
       </c>
       <c r="R7" t="n">
-        <v>6631964</v>
+        <v>6632307</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1418,22 +1384,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-03-31</t>
+          <t>2020-02-22</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-02-22</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2020-03-31</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>18:00</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På grusvägen</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1444,16 +1415,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Tallhällmark</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1466,16 +1427,20 @@
           <t>Pia Hagfors</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Skogsprojektet</t>
+        </is>
+      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/84024850</t>
+          <t>https://artportalen.se/Sighting/82321237</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>84024890</v>
+        <v>82321521</v>
       </c>
       <c r="B8" t="n">
         <v>57141</v>
@@ -1508,7 +1473,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1518,17 +1483,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>St Björksnarssjön Ö skogen, Ramnäs, Vstm, Vstm</t>
+          <t>Målsjöv-Stora Björksnarssjön, Ramnsä, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559052</v>
+        <v>559145</v>
       </c>
       <c r="R8" t="n">
-        <v>6631966</v>
+        <v>6632322</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1552,22 +1517,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-03-31</t>
+          <t>2020-02-22</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2020-02-22</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2020-03-31</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>18:00</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På grusvägen</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1578,16 +1548,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Stenhäll i tallhällmark</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1600,16 +1560,20 @@
           <t>Pia Hagfors</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Skogsprojektet</t>
+        </is>
+      </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/84024890</t>
+          <t>https://artportalen.se/Sighting/82321521</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>84024932</v>
+        <v>84024850</v>
       </c>
       <c r="B9" t="n">
         <v>57141</v>
@@ -1659,7 +1623,7 @@
         <v>559053</v>
       </c>
       <c r="R9" t="n">
-        <v>6631972</v>
+        <v>6631964</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1720,7 +1684,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Stenhäll i tallhällmark</t>
+          <t>Tallhällmark</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1737,13 +1701,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/84024932</t>
+          <t>https://artportalen.se/Sighting/84024850</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>84024944</v>
+        <v>84024890</v>
       </c>
       <c r="B10" t="n">
         <v>57141</v>
@@ -1790,10 +1754,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559051</v>
+        <v>559052</v>
       </c>
       <c r="R10" t="n">
-        <v>6631977</v>
+        <v>6631966</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1854,7 +1818,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Tallhällmark</t>
+          <t>Stenhäll i tallhällmark</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1871,13 +1835,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/84024944</t>
+          <t>https://artportalen.se/Sighting/84024890</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>84024971</v>
+        <v>84024932</v>
       </c>
       <c r="B11" t="n">
         <v>57141</v>
@@ -1924,10 +1888,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559159</v>
+        <v>559053</v>
       </c>
       <c r="R11" t="n">
-        <v>6631970</v>
+        <v>6631972</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1988,7 +1952,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Hällmark med gamla tallar, blåbärsris</t>
+          <t>Stenhäll i tallhällmark</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2005,13 +1969,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/84024971</t>
+          <t>https://artportalen.se/Sighting/84024932</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>84024981</v>
+        <v>84024944</v>
       </c>
       <c r="B12" t="n">
         <v>57141</v>
@@ -2044,7 +2008,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>funnen död</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2054,14 +2018,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>St Björksnarssjön Ö skogen, Ramnäs, Vstm</t>
+          <t>St Björksnarssjön Ö skogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>559163</v>
+        <v>559051</v>
       </c>
       <c r="R12" t="n">
-        <v>6631975</v>
+        <v>6631977</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -2106,11 +2070,6 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Flera fjädrar kvar efter dödad tjäder</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2127,7 +2086,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Tallhällmarksskog</t>
+          <t>Tallhällmark</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2144,13 +2103,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/84024981</t>
+          <t>https://artportalen.se/Sighting/84024944</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>84024991</v>
+        <v>84024971</v>
       </c>
       <c r="B13" t="n">
         <v>57141</v>
@@ -2197,10 +2156,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559165</v>
+        <v>559159</v>
       </c>
       <c r="R13" t="n">
-        <v>6632041</v>
+        <v>6631970</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -2261,7 +2220,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Tallhällmarksskog</t>
+          <t>Hällmark med gamla tallar, blåbärsris</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2278,13 +2237,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/84024991</t>
+          <t>https://artportalen.se/Sighting/84024971</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>84024998</v>
+        <v>84024981</v>
       </c>
       <c r="B14" t="n">
         <v>57141</v>
@@ -2317,7 +2276,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>funnen död</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2327,14 +2286,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>St Björksnarssjön Ö skogen, Ramnäs, Vstm, Vstm</t>
+          <t>St Björksnarssjön Ö skogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559151</v>
+        <v>559163</v>
       </c>
       <c r="R14" t="n">
-        <v>6632042</v>
+        <v>6631975</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2379,6 +2338,11 @@
           <t>18:00</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Flera fjädrar kvar efter dödad tjäder</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2412,13 +2376,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/84024998</t>
+          <t>https://artportalen.se/Sighting/84024981</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>84025004</v>
+        <v>84024991</v>
       </c>
       <c r="B15" t="n">
         <v>57141</v>
@@ -2465,10 +2429,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559146</v>
+        <v>559165</v>
       </c>
       <c r="R15" t="n">
-        <v>6632049</v>
+        <v>6632041</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2546,13 +2510,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/84025004</t>
+          <t>https://artportalen.se/Sighting/84024991</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>84025021</v>
+        <v>84024998</v>
       </c>
       <c r="B16" t="n">
         <v>57141</v>
@@ -2599,10 +2563,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>559173</v>
+        <v>559151</v>
       </c>
       <c r="R16" t="n">
-        <v>6632106</v>
+        <v>6632042</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2663,7 +2627,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Tallhällmarksskog med gamla tallar</t>
+          <t>Tallhällmarksskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2680,13 +2644,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/84025021</t>
+          <t>https://artportalen.se/Sighting/84024998</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>84025030</v>
+        <v>84025004</v>
       </c>
       <c r="B17" t="n">
         <v>57141</v>
@@ -2733,10 +2697,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>559262</v>
+        <v>559146</v>
       </c>
       <c r="R17" t="n">
-        <v>6632107</v>
+        <v>6632049</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2781,11 +2745,6 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Vid tallraka</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2819,13 +2778,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/84025030</t>
+          <t>https://artportalen.se/Sighting/84025004</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>84025051</v>
+        <v>84025021</v>
       </c>
       <c r="B18" t="n">
         <v>57141</v>
@@ -2872,13 +2831,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559289</v>
+        <v>559173</v>
       </c>
       <c r="R18" t="n">
-        <v>6632110</v>
+        <v>6632106</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2936,7 +2895,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Tallhällmarksskog med gamla tallar, natträd</t>
+          <t>Tallhällmarksskog med gamla tallar</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2953,13 +2912,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/84025051</t>
+          <t>https://artportalen.se/Sighting/84025021</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>84025062</v>
+        <v>84025030</v>
       </c>
       <c r="B19" t="n">
         <v>57141</v>
@@ -3006,10 +2965,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559288</v>
+        <v>559262</v>
       </c>
       <c r="R19" t="n">
-        <v>6632104</v>
+        <v>6632107</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -3054,6 +3013,11 @@
           <t>18:00</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Vid tallraka</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -3070,7 +3034,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Tallhällmarksskog med gamla tallar, natträd</t>
+          <t>Tallhällmarksskog</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3087,13 +3051,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/84025062</t>
+          <t>https://artportalen.se/Sighting/84025030</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>84025077</v>
+        <v>84025051</v>
       </c>
       <c r="B20" t="n">
         <v>57141</v>
@@ -3143,10 +3107,10 @@
         <v>559289</v>
       </c>
       <c r="R20" t="n">
-        <v>6632105</v>
+        <v>6632110</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3204,7 +3168,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Hällmarksskog med tallar</t>
+          <t>Tallhällmarksskog med gamla tallar, natträd</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3221,13 +3185,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/84025077</t>
+          <t>https://artportalen.se/Sighting/84025051</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>84025088</v>
+        <v>84025062</v>
       </c>
       <c r="B21" t="n">
         <v>57141</v>
@@ -3274,10 +3238,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>559298</v>
+        <v>559288</v>
       </c>
       <c r="R21" t="n">
-        <v>6632101</v>
+        <v>6632104</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -3338,7 +3302,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Hällmarksskog tall</t>
+          <t>Tallhällmarksskog med gamla tallar, natträd</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3355,13 +3319,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/84025088</t>
+          <t>https://artportalen.se/Sighting/84025062</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>84025110</v>
+        <v>84025077</v>
       </c>
       <c r="B22" t="n">
         <v>57141</v>
@@ -3408,10 +3372,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>559297</v>
+        <v>559289</v>
       </c>
       <c r="R22" t="n">
-        <v>6632107</v>
+        <v>6632105</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3472,7 +3436,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Tallhällmarksskog</t>
+          <t>Hällmarksskog med tallar</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3489,13 +3453,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/84025110</t>
+          <t>https://artportalen.se/Sighting/84025077</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>84025123</v>
+        <v>84025088</v>
       </c>
       <c r="B23" t="n">
         <v>57141</v>
@@ -3542,10 +3506,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>559347</v>
+        <v>559298</v>
       </c>
       <c r="R23" t="n">
-        <v>6632111</v>
+        <v>6632101</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3606,7 +3570,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Tallhällmarksskog med gamla tallar</t>
+          <t>Hällmarksskog tall</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3623,13 +3587,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/84025123</t>
+          <t>https://artportalen.se/Sighting/84025088</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>84025145</v>
+        <v>84025110</v>
       </c>
       <c r="B24" t="n">
         <v>57141</v>
@@ -3676,10 +3640,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>559326</v>
+        <v>559297</v>
       </c>
       <c r="R24" t="n">
-        <v>6632166</v>
+        <v>6632107</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3740,7 +3704,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Tallhällmarksskog med gamla tallar</t>
+          <t>Tallhällmarksskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3757,13 +3721,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/84025145</t>
+          <t>https://artportalen.se/Sighting/84025110</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>84025155</v>
+        <v>84025123</v>
       </c>
       <c r="B25" t="n">
         <v>57141</v>
@@ -3810,10 +3774,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>559324</v>
+        <v>559347</v>
       </c>
       <c r="R25" t="n">
-        <v>6632175</v>
+        <v>6632111</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3874,7 +3838,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Tallhällmarksskog</t>
+          <t>Tallhällmarksskog med gamla tallar</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3891,13 +3855,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/84025155</t>
+          <t>https://artportalen.se/Sighting/84025123</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>84025194</v>
+        <v>84025145</v>
       </c>
       <c r="B26" t="n">
         <v>57141</v>
@@ -3944,10 +3908,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>559279</v>
+        <v>559326</v>
       </c>
       <c r="R26" t="n">
-        <v>6632175</v>
+        <v>6632166</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -4008,7 +3972,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Tallhällmarksskog</t>
+          <t>Tallhällmarksskog med gamla tallar</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4025,13 +3989,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/84025194</t>
+          <t>https://artportalen.se/Sighting/84025145</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>84025210</v>
+        <v>84025155</v>
       </c>
       <c r="B27" t="n">
         <v>57141</v>
@@ -4078,13 +4042,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>559276</v>
+        <v>559324</v>
       </c>
       <c r="R27" t="n">
-        <v>6632181</v>
+        <v>6632175</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4142,7 +4106,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Tallhällmarksskog med gamla tallar, natträd</t>
+          <t>Tallhällmarksskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4159,13 +4123,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/84025210</t>
+          <t>https://artportalen.se/Sighting/84025155</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>84025224</v>
+        <v>84025194</v>
       </c>
       <c r="B28" t="n">
         <v>57141</v>
@@ -4212,10 +4176,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>559267</v>
+        <v>559279</v>
       </c>
       <c r="R28" t="n">
-        <v>6632179</v>
+        <v>6632175</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -4293,13 +4257,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/84025224</t>
+          <t>https://artportalen.se/Sighting/84025194</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>84025240</v>
+        <v>84025210</v>
       </c>
       <c r="B29" t="n">
         <v>57141</v>
@@ -4346,13 +4310,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>559267</v>
+        <v>559276</v>
       </c>
       <c r="R29" t="n">
-        <v>6632185</v>
+        <v>6632181</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4410,7 +4374,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Tallhällmarksskog, natträd</t>
+          <t>Tallhällmarksskog med gamla tallar, natträd</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4427,13 +4391,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/84025240</t>
+          <t>https://artportalen.se/Sighting/84025210</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>84025262</v>
+        <v>84025224</v>
       </c>
       <c r="B30" t="n">
         <v>57141</v>
@@ -4480,10 +4444,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>559224</v>
+        <v>559267</v>
       </c>
       <c r="R30" t="n">
-        <v>6632202</v>
+        <v>6632179</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -4544,7 +4508,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Hällmarker med gamla tallar</t>
+          <t>Tallhällmarksskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4561,13 +4525,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/84025262</t>
+          <t>https://artportalen.se/Sighting/84025224</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>84025287</v>
+        <v>84025240</v>
       </c>
       <c r="B31" t="n">
         <v>57141</v>
@@ -4614,10 +4578,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>559171</v>
+        <v>559267</v>
       </c>
       <c r="R31" t="n">
-        <v>6632172</v>
+        <v>6632185</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -4678,7 +4642,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Hällmarker med tall</t>
+          <t>Tallhällmarksskog, natträd</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4695,13 +4659,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/84025287</t>
+          <t>https://artportalen.se/Sighting/84025240</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>84025304</v>
+        <v>84025262</v>
       </c>
       <c r="B32" t="n">
         <v>57141</v>
@@ -4737,17 +4701,21 @@
           <t>färsk spillning</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>St Björksnarssjön Ö skogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>559150</v>
+        <v>559224</v>
       </c>
       <c r="R32" t="n">
-        <v>6632179</v>
+        <v>6632202</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4808,7 +4776,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Tallhällmarksskog</t>
+          <t>Hällmarker med gamla tallar</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4825,13 +4793,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/84025304</t>
+          <t>https://artportalen.se/Sighting/84025262</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>84025315</v>
+        <v>84025287</v>
       </c>
       <c r="B33" t="n">
         <v>57141</v>
@@ -4867,17 +4835,21 @@
           <t>färsk spillning</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>St Björksnarssjön Ö skogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>559150</v>
+        <v>559171</v>
       </c>
       <c r="R33" t="n">
-        <v>6632184</v>
+        <v>6632172</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4938,7 +4910,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Tallhällmarksskog</t>
+          <t>Hällmarker med tall</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4955,16 +4927,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/84025315</t>
+          <t>https://artportalen.se/Sighting/84025287</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112500444</v>
+        <v>84025304</v>
       </c>
       <c r="B34" t="n">
-        <v>5009</v>
+        <v>57141</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4972,42 +4944,45 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>101284</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sotpraktbagge</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Melanophila acuminata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(De Geer, 1774)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Björksnarsjön, bränt 2022, Vstm</t>
+          <t>St Björksnarssjön Ö skogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>559218</v>
+        <v>559150</v>
       </c>
       <c r="R34" t="n">
-        <v>6631982</v>
+        <v>6632179</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5031,17 +5006,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
+          <t>2020-03-31</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Gnagspår, troligen kvar i ved, bark borthackad. Även rikligt med tallbock, färska kläckhål, vilket är extremt tidigt</t>
+          <t>2020-03-31</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5053,44 +5033,40 @@
       <c r="AG34" t="b">
         <v>0</v>
       </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Äldre tallskog ca 110 år, ställvis yngre tall, delvis slutavverkat, inslag av hällmark, gran</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Grovbarkig gran med rejäla rotben, i hyggeskant</t>
+          <t>Tallhällmarksskog</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av vedlevande evertebrater</t>
-        </is>
-      </c>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112500444</t>
+          <t>https://artportalen.se/Sighting/84025304</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112500446</v>
+        <v>84025315</v>
       </c>
       <c r="B35" t="n">
-        <v>5009</v>
+        <v>57141</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5098,42 +5074,45 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>101284</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sotpraktbagge</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Melanophila acuminata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(De Geer, 1774)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Björksnarsjön, bränt 2022, Vstm</t>
+          <t>St Björksnarssjön Ö skogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>559155</v>
+        <v>559150</v>
       </c>
       <c r="R35" t="n">
-        <v>6632218</v>
+        <v>6632184</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5157,17 +5136,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
+          <t>2020-03-31</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Gnagspår rikliga, troligen kvar i ved, bark borthackad</t>
+          <t>2020-03-31</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5179,44 +5163,40 @@
       <c r="AG35" t="b">
         <v>0</v>
       </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Äldre tallskog ca 110 år, ställvis yngre tall, delvis slutavverkat, inslag av hällmark, gran</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Rotben, tall 45 cm, stående på häll</t>
+          <t>Tallhällmarksskog</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av vedlevande evertebrater</t>
-        </is>
-      </c>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112500446</t>
+          <t>https://artportalen.se/Sighting/84025315</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>79433343</v>
+        <v>112500444</v>
       </c>
       <c r="B36" t="n">
-        <v>8455</v>
+        <v>5009</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5224,46 +5204,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>101284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Sotpraktbagge</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Melanophila acuminata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(De Geer, 1774)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Stora Björksnarssjön O, Vstm</t>
+          <t>Björksnarsjön, bränt 2022, Vstm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>559227</v>
+        <v>559218</v>
       </c>
       <c r="R36" t="n">
-        <v>6632115</v>
+        <v>6631982</v>
       </c>
       <c r="S36" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5287,22 +5263,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2019-08-15</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>10:40</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2019-08-15</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>10:40</t>
+          <t>2023-06-06</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Gnagspår, troligen kvar i ved, bark borthackad. Även rikligt med tallbock, färska kläckhål, vilket är extremt tidigt</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5311,44 +5282,47 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
+          <t>Äldre tallskog ca 110 år, ställvis yngre tall, delvis slutavverkat, inslag av hällmark, gran</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Grova markliggande tallgrenar</t>
+          <t>Grovbarkig gran med rejäla rotben, i hyggeskant</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
+          <t>Lars-Ove Wikars</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av vedlevande evertebrater</t>
+        </is>
+      </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79433343</t>
+          <t>https://artportalen.se/Sighting/112500444</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112500447</v>
+        <v>112500446</v>
       </c>
       <c r="B37" t="n">
-        <v>8455</v>
+        <v>5009</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5356,21 +5330,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>101284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Sotpraktbagge</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Melanophila acuminata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(De Geer, 1774)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5385,10 +5359,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>559250</v>
+        <v>559155</v>
       </c>
       <c r="R37" t="n">
-        <v>6632201</v>
+        <v>6632218</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5425,7 +5399,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikliga gångsystem. Även större märgborre, samt Pytho</t>
+          <t>Gnagspår rikliga, troligen kvar i ved, bark borthackad</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5444,7 +5418,7 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Tallvindfälle innan bränning</t>
+          <t>Rotben, tall 45 cm, stående på häll</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5465,13 +5439,13 @@
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112500447</t>
+          <t>https://artportalen.se/Sighting/112500446</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130342994</v>
+        <v>79433343</v>
       </c>
       <c r="B38" t="n">
         <v>8455</v>
@@ -5500,19 +5474,28 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Stora Björksnarssjön, Ö om, Vstm</t>
+          <t>Stora Björksnarssjön O, Vstm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>559164</v>
+        <v>559227</v>
       </c>
       <c r="R38" t="n">
-        <v>6632207</v>
+        <v>6632115</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5536,17 +5519,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2019-08-15</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Naturvärdesbedömning Gysinge skog.</t>
+          <t>2019-08-15</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5555,90 +5543,84 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>äldre tallskog</t>
+          <t>Hällmarkstallskog</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>Grova markliggande tallgrenar</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Jenny Andersson, Carl A Andersson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130342994</t>
+          <t>https://artportalen.se/Sighting/79433343</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>105379369</v>
+        <v>112500447</v>
       </c>
       <c r="B39" t="n">
-        <v>56522</v>
+        <v>8455</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>206004</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stora Björksnarssjön, Ramnäs sn, Vstm</t>
+          <t>Björksnarsjön, bränt 2022, Vstm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>559267</v>
+        <v>559250</v>
       </c>
       <c r="R39" t="n">
-        <v>6632019</v>
+        <v>6632201</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5665,27 +5647,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2022-12-28</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2022-12-28</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>2 individer tillsammans  av 5 löpor mot S. Hyggesbränna</t>
+          <t>Rikliga gångsystem. Även större märgborre, samt Pytho</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5696,81 +5668,83 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Äldre tallskog ca 110 år, ställvis yngre tall, delvis slutavverkat, inslag av hällmark, gran</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Tallvindfälle innan bränning</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Sören Larsson, Greta Larsson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
+          <t>Lars-Ove Wikars</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av vedlevande evertebrater</t>
+        </is>
+      </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105379369</t>
+          <t>https://artportalen.se/Sighting/112500447</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>105379396</v>
+        <v>130342994</v>
       </c>
       <c r="B40" t="n">
-        <v>56522</v>
+        <v>8455</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>206004</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stora Björksnarssjön, Ramnäs sn, Vstm</t>
+          <t>Stora Björksnarssjön, Ö om, Vstm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>559247</v>
+        <v>559164</v>
       </c>
       <c r="R40" t="n">
-        <v>6632262</v>
+        <v>6632207</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5794,27 +5768,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2022-12-28</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2022-12-28</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>En ensam hare löpa mot S. Samtliga harar har beat på uppstickande gröna blåbärsris. Hyggesbränna</t>
+          <t>Naturvärdesbedömning Gysinge skog.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5825,81 +5789,88 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>äldre tallskog</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>tallåga</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Sören Larsson, Greta Larsson</t>
+          <t>Jenny Andersson, Carl A Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105379396</t>
+          <t>https://artportalen.se/Sighting/130342994</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>105379413</v>
+        <v>136640201</v>
       </c>
       <c r="B41" t="n">
-        <v>56522</v>
+        <v>8463</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>206004</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stora Björksnarssjön, Ramnäs sn, Vstm</t>
+          <t>Stora Björksnarssjön O, Vstm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>559140</v>
+        <v>559107</v>
       </c>
       <c r="R41" t="n">
-        <v>6632133</v>
+        <v>6632136</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5923,27 +5894,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2022-12-28</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2022-12-28</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ensam hare löpa mot söder. Betat på uppstickande blåbärsris. Hyggesbränna</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5952,24 +5908,763 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Naturvårdsbränt hygge/tallskog</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Sören Larsson, Greta Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136640201</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>105379369</v>
+      </c>
+      <c r="B42" t="n">
+        <v>56522</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Stora Björksnarssjön, Ramnäs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>559267</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6632019</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2022-12-28</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2022-12-28</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>2 individer tillsammans  av 5 löpor mot S. Hyggesbränna</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Sören Larsson, Greta Larsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105379369</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>105379396</v>
+      </c>
+      <c r="B43" t="n">
+        <v>56522</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Stora Björksnarssjön, Ramnäs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>559247</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6632262</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2022-12-28</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2022-12-28</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>En ensam hare löpa mot S. Samtliga harar har beat på uppstickande gröna blåbärsris. Hyggesbränna</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Sören Larsson, Greta Larsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105379396</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>105379413</v>
+      </c>
+      <c r="B44" t="n">
+        <v>56522</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Stora Björksnarssjön, Ramnäs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>559140</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6632133</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2022-12-28</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2022-12-28</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ensam hare löpa mot söder. Betat på uppstickande blåbärsris. Hyggesbränna</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Sören Larsson, Greta Larsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/105379413</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>136640260</v>
+      </c>
+      <c r="B45" t="n">
+        <v>108367</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Stora Björksnarssjön O, Vstm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>559107</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6632136</v>
+      </c>
+      <c r="S45" t="n">
+        <v>100</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Naturvårdsbränt hygge/tallskog</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136640260</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>136640225</v>
+      </c>
+      <c r="B46" t="n">
+        <v>106358</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>221154</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Skogsstjärna</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Lysimachia europaea</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) U. Manns &amp; Anderb.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Stora Björksnarssjön O, Vstm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>559107</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6632136</v>
+      </c>
+      <c r="S46" t="n">
+        <v>100</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Naturvårdsbränt hygge/tallskog</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136640225</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>136640189</v>
+      </c>
+      <c r="B47" t="n">
+        <v>106517</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>221157</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Blåbär</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Vaccinium myrtillus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Stora Björksnarssjön O, Vstm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>559107</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6632136</v>
+      </c>
+      <c r="S47" t="n">
+        <v>100</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Naturvårdsbränt hygge/tallskog</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136640189</t>
         </is>
       </c>
     </row>
@@ -6015,6 +6710,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 42-2022 artfynd.xlsx
+++ b/artfynd/S 42-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136640141</v>
       </c>
       <c r="B2" t="n">
-        <v>92316</v>
+        <v>92319</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136640147</v>
       </c>
       <c r="B3" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>136640260</v>
       </c>
       <c r="B45" t="n">
-        <v>108367</v>
+        <v>108370</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>136640225</v>
       </c>
       <c r="B46" t="n">
-        <v>106358</v>
+        <v>106361</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>136640189</v>
       </c>
       <c r="B47" t="n">
-        <v>106517</v>
+        <v>106520</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/S 42-2022 artfynd.xlsx
+++ b/artfynd/S 42-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136640141</v>
       </c>
       <c r="B2" t="n">
-        <v>92319</v>
+        <v>92320</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136640147</v>
       </c>
       <c r="B3" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>136640260</v>
       </c>
       <c r="B45" t="n">
-        <v>108370</v>
+        <v>108371</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>136640225</v>
       </c>
       <c r="B46" t="n">
-        <v>106361</v>
+        <v>106362</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>136640189</v>
       </c>
       <c r="B47" t="n">
-        <v>106520</v>
+        <v>106521</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/S 42-2022 artfynd.xlsx
+++ b/artfynd/S 42-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136640141</v>
       </c>
       <c r="B2" t="n">
-        <v>92320</v>
+        <v>92325</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136640147</v>
       </c>
       <c r="B3" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>136640260</v>
       </c>
       <c r="B45" t="n">
-        <v>108371</v>
+        <v>108376</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>136640225</v>
       </c>
       <c r="B46" t="n">
-        <v>106362</v>
+        <v>106367</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>136640189</v>
       </c>
       <c r="B47" t="n">
-        <v>106521</v>
+        <v>106526</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/S 42-2022 artfynd.xlsx
+++ b/artfynd/S 42-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136640141</v>
       </c>
       <c r="B2" t="n">
-        <v>92325</v>
+        <v>92327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136640147</v>
       </c>
       <c r="B3" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>136640260</v>
       </c>
       <c r="B45" t="n">
-        <v>108376</v>
+        <v>108378</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>136640225</v>
       </c>
       <c r="B46" t="n">
-        <v>106367</v>
+        <v>106369</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>136640189</v>
       </c>
       <c r="B47" t="n">
-        <v>106526</v>
+        <v>106528</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/S 42-2022 artfynd.xlsx
+++ b/artfynd/S 42-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136640141</v>
       </c>
       <c r="B2" t="n">
-        <v>92327</v>
+        <v>92329</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136640147</v>
       </c>
       <c r="B3" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>136640260</v>
       </c>
       <c r="B45" t="n">
-        <v>108378</v>
+        <v>108384</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>136640225</v>
       </c>
       <c r="B46" t="n">
-        <v>106369</v>
+        <v>106375</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>136640189</v>
       </c>
       <c r="B47" t="n">
-        <v>106528</v>
+        <v>106534</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/S 42-2022 artfynd.xlsx
+++ b/artfynd/S 42-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136640141</v>
       </c>
       <c r="B2" t="n">
-        <v>92329</v>
+        <v>92331</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136640147</v>
       </c>
       <c r="B3" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>136640260</v>
       </c>
       <c r="B45" t="n">
-        <v>108384</v>
+        <v>108386</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>136640225</v>
       </c>
       <c r="B46" t="n">
-        <v>106375</v>
+        <v>106377</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>136640189</v>
       </c>
       <c r="B47" t="n">
-        <v>106534</v>
+        <v>106536</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/S 42-2022 artfynd.xlsx
+++ b/artfynd/S 42-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136640141</v>
       </c>
       <c r="B2" t="n">
-        <v>92331</v>
+        <v>92332</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136640147</v>
       </c>
       <c r="B3" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>136640260</v>
       </c>
       <c r="B45" t="n">
-        <v>108386</v>
+        <v>108387</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>136640225</v>
       </c>
       <c r="B46" t="n">
-        <v>106377</v>
+        <v>106378</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>136640189</v>
       </c>
       <c r="B47" t="n">
-        <v>106536</v>
+        <v>106537</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/S 42-2022 artfynd.xlsx
+++ b/artfynd/S 42-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136640141</v>
       </c>
       <c r="B2" t="n">
-        <v>92332</v>
+        <v>92338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136640147</v>
       </c>
       <c r="B3" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>136640260</v>
       </c>
       <c r="B45" t="n">
-        <v>108387</v>
+        <v>108393</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>136640225</v>
       </c>
       <c r="B46" t="n">
-        <v>106378</v>
+        <v>106384</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>136640189</v>
       </c>
       <c r="B47" t="n">
-        <v>106537</v>
+        <v>106543</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/S 42-2022 artfynd.xlsx
+++ b/artfynd/S 42-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136640141</v>
       </c>
       <c r="B2" t="n">
-        <v>92338</v>
+        <v>92342</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136640147</v>
       </c>
       <c r="B3" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>136640260</v>
       </c>
       <c r="B45" t="n">
-        <v>108393</v>
+        <v>108397</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>136640225</v>
       </c>
       <c r="B46" t="n">
-        <v>106384</v>
+        <v>106388</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>136640189</v>
       </c>
       <c r="B47" t="n">
-        <v>106543</v>
+        <v>106547</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/S 42-2022 artfynd.xlsx
+++ b/artfynd/S 42-2022 artfynd.xlsx
@@ -6332,7 +6332,7 @@
         <v>136640260</v>
       </c>
       <c r="B45" t="n">
-        <v>108397</v>
+        <v>108399</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>136640225</v>
       </c>
       <c r="B46" t="n">
-        <v>106388</v>
+        <v>106390</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>136640189</v>
       </c>
       <c r="B47" t="n">
-        <v>106547</v>
+        <v>106549</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/S 42-2022 artfynd.xlsx
+++ b/artfynd/S 42-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136640141</v>
       </c>
       <c r="B2" t="n">
-        <v>92342</v>
+        <v>92344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136640147</v>
       </c>
       <c r="B3" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>136640260</v>
       </c>
       <c r="B45" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>136640225</v>
       </c>
       <c r="B46" t="n">
-        <v>106390</v>
+        <v>106392</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>136640189</v>
       </c>
       <c r="B47" t="n">
-        <v>106549</v>
+        <v>106551</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/S 42-2022 artfynd.xlsx
+++ b/artfynd/S 42-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136640141</v>
       </c>
       <c r="B2" t="n">
-        <v>92344</v>
+        <v>92357</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136640147</v>
       </c>
       <c r="B3" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>136640260</v>
       </c>
       <c r="B45" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>136640225</v>
       </c>
       <c r="B46" t="n">
-        <v>106392</v>
+        <v>106405</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>136640189</v>
       </c>
       <c r="B47" t="n">
-        <v>106551</v>
+        <v>106564</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/S 42-2022 artfynd.xlsx
+++ b/artfynd/S 42-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136640141</v>
       </c>
       <c r="B2" t="n">
-        <v>92357</v>
+        <v>92359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136640147</v>
       </c>
       <c r="B3" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         <v>136640201</v>
       </c>
       <c r="B41" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>136640260</v>
       </c>
       <c r="B45" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>136640225</v>
       </c>
       <c r="B46" t="n">
-        <v>106405</v>
+        <v>106407</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>136640189</v>
       </c>
       <c r="B47" t="n">
-        <v>106564</v>
+        <v>106566</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
